--- a/StructureDefinition-SEEHDSConditionDiagnosis.xlsx
+++ b/StructureDefinition-SEEHDSConditionDiagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:04:04+00:00</t>
+    <t>2026-10-06T07:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSConditionDiagnosis.xlsx
+++ b/StructureDefinition-SEEHDSConditionDiagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:20:43+00:00</t>
+    <t>2026-10-07T11:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSConditionDiagnosis.xlsx
+++ b/StructureDefinition-SEEHDSConditionDiagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:41:58+00:00</t>
+    <t>2026-10-07T11:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSConditionDiagnosis.xlsx
+++ b/StructureDefinition-SEEHDSConditionDiagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:49:57+00:00</t>
+    <t>2026-10-09T07:52:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSConditionDiagnosis.xlsx
+++ b/StructureDefinition-SEEHDSConditionDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.3</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T07:52:45+00:00</t>
+    <t>2026-10-12T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSConditionDiagnosis.xlsx
+++ b/StructureDefinition-SEEHDSConditionDiagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:51:47+00:00</t>
+    <t>2026-10-12T13:38:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSConditionDiagnosis.xlsx
+++ b/StructureDefinition-SEEHDSConditionDiagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:38:08+00:00</t>
+    <t>2026-10-15T17:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSConditionDiagnosis.xlsx
+++ b/StructureDefinition-SEEHDSConditionDiagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T17:10:15+00:00</t>
+    <t>2026-10-15T18:03:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSConditionDiagnosis.xlsx
+++ b/StructureDefinition-SEEHDSConditionDiagnosis.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$109</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4011" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4167" uniqueCount="613">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T18:03:33+00:00</t>
+    <t>2026-10-26T15:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1622,6 +1622,42 @@
   </si>
   <si>
     <t>Onset of the symptom, complaint, functional limitation, complication or date of diagnosis. A ‘vague’ date, such as only the year or the month and the year, is permitted.</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]:onsetAge</t>
+  </si>
+  <si>
+    <t>onsetAge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age
+</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]:onsetPeriod</t>
+  </si>
+  <si>
+    <t>onsetPeriod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]:onsetRange</t>
+  </si>
+  <si>
+    <t>onsetRange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Range
+</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]:onsetString</t>
+  </si>
+  <si>
+    <t>onsetString</t>
   </si>
   <si>
     <t>Condition.abatement[x]</t>
@@ -2214,7 +2250,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP105"/>
+  <dimension ref="A1:AP109"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.34765625" customWidth="true" bestFit="true"/>
@@ -12573,9 +12609,11 @@
         <v>514</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="C87" s="2"/>
+        <v>499</v>
+      </c>
+      <c r="C87" t="s" s="2">
+        <v>515</v>
+      </c>
       <c r="D87" t="s" s="2">
         <v>79</v>
       </c>
@@ -12593,19 +12631,19 @@
         <v>79</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>500</v>
+        <v>516</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>515</v>
+        <v>501</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>516</v>
+        <v>502</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>517</v>
+        <v>503</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12643,17 +12681,19 @@
         <v>79</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="AC87" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>514</v>
+        <v>499</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12662,25 +12702,25 @@
         <v>91</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>518</v>
+        <v>79</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>79</v>
+        <v>506</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>79</v>
+        <v>507</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>519</v>
+        <v>508</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>520</v>
+        <v>509</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>79</v>
@@ -12688,13 +12728,13 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>514</v>
+        <v>499</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>79</v>
@@ -12713,19 +12753,19 @@
         <v>79</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>215</v>
+        <v>519</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>515</v>
+        <v>501</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>523</v>
+        <v>502</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>517</v>
+        <v>503</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12775,7 +12815,7 @@
         <v>79</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>514</v>
+        <v>499</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12784,38 +12824,40 @@
         <v>91</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>518</v>
+        <v>79</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>79</v>
+        <v>506</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>79</v>
+        <v>507</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>519</v>
+        <v>508</v>
       </c>
       <c r="AO88" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AP88" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="89" hidden="true">
+      <c r="A89" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="AP88" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s" s="2">
-        <v>524</v>
-      </c>
       <c r="B89" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="C89" s="2"/>
+        <v>499</v>
+      </c>
+      <c r="C89" t="s" s="2">
+        <v>521</v>
+      </c>
       <c r="D89" t="s" s="2">
         <v>79</v>
       </c>
@@ -12827,7 +12869,7 @@
         <v>91</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>79</v>
@@ -12836,15 +12878,17 @@
         <v>92</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>215</v>
+        <v>522</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>525</v>
+        <v>501</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="N89" s="2"/>
+        <v>502</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>503</v>
+      </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>79</v>
@@ -12893,7 +12937,7 @@
         <v>79</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>524</v>
+        <v>499</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12908,32 +12952,34 @@
         <v>103</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>79</v>
+        <v>506</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>527</v>
+        <v>507</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>528</v>
+        <v>508</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>529</v>
+        <v>509</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="C90" s="2"/>
+        <v>499</v>
+      </c>
+      <c r="C90" t="s" s="2">
+        <v>524</v>
+      </c>
       <c r="D90" t="s" s="2">
         <v>79</v>
       </c>
@@ -12945,7 +12991,7 @@
         <v>91</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>79</v>
@@ -12954,15 +13000,17 @@
         <v>92</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>531</v>
+        <v>105</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>532</v>
+        <v>501</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N90" s="2"/>
+        <v>502</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>503</v>
+      </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>79</v>
@@ -13011,7 +13059,7 @@
         <v>79</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>530</v>
+        <v>499</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13026,30 +13074,30 @@
         <v>103</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>79</v>
+        <v>506</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>79</v>
+        <v>507</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>534</v>
+        <v>508</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>535</v>
+        <v>509</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>536</v>
+        <v>525</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>536</v>
+        <v>525</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13063,24 +13111,26 @@
         <v>91</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>531</v>
+        <v>500</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>537</v>
+        <v>526</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="N91" s="2"/>
+        <v>527</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>528</v>
+      </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>79</v>
@@ -13117,19 +13167,17 @@
         <v>79</v>
       </c>
       <c r="AB91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>504</v>
+      </c>
+      <c r="AC91" s="2"/>
       <c r="AD91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE91" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>536</v>
+        <v>525</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13138,7 +13186,7 @@
         <v>91</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>79</v>
+        <v>529</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>103</v>
@@ -13150,13 +13198,13 @@
         <v>79</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>539</v>
+        <v>79</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>79</v>
@@ -13164,12 +13212,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="C92" s="2"/>
+        <v>525</v>
+      </c>
+      <c r="C92" t="s" s="2">
+        <v>533</v>
+      </c>
       <c r="D92" t="s" s="2">
         <v>79</v>
       </c>
@@ -13178,7 +13228,7 @@
         <v>80</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>79</v>
@@ -13190,15 +13240,17 @@
         <v>79</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>543</v>
+        <v>215</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>544</v>
+        <v>526</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="N92" s="2"/>
+        <v>534</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>528</v>
+      </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>79</v>
@@ -13247,19 +13299,19 @@
         <v>79</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>542</v>
+        <v>525</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>79</v>
+        <v>529</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>546</v>
+        <v>103</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>79</v>
@@ -13271,21 +13323,21 @@
         <v>79</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>547</v>
+        <v>530</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>79</v>
+        <v>531</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="93" hidden="true">
+    <row r="93">
       <c r="A93" t="s" s="2">
-        <v>548</v>
+        <v>535</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>548</v>
+        <v>535</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13299,22 +13351,22 @@
         <v>91</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>105</v>
+        <v>215</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>106</v>
+        <v>536</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>107</v>
+        <v>537</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13365,7 +13417,7 @@
         <v>79</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>108</v>
+        <v>535</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13377,7 +13429,7 @@
         <v>79</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>79</v>
@@ -13386,57 +13438,55 @@
         <v>79</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>79</v>
+        <v>538</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>109</v>
+        <v>539</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>79</v>
+        <v>540</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="94" hidden="true">
+    <row r="94">
       <c r="A94" t="s" s="2">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H94" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>112</v>
+        <v>542</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>113</v>
+        <v>543</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>544</v>
+      </c>
+      <c r="N94" s="2"/>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>79</v>
@@ -13485,19 +13535,19 @@
         <v>79</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>119</v>
+        <v>541</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>79</v>
@@ -13509,57 +13559,53 @@
         <v>79</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>109</v>
+        <v>545</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>79</v>
+        <v>546</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="95" hidden="true">
+    <row r="95">
       <c r="A95" t="s" s="2">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>551</v>
+        <v>79</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I95" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="J95" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>112</v>
+        <v>542</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>549</v>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>79</v>
       </c>
@@ -13607,19 +13653,19 @@
         <v>79</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>79</v>
@@ -13628,13 +13674,13 @@
         <v>79</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>79</v>
+        <v>550</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>190</v>
+        <v>551</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>79</v>
+        <v>552</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>79</v>
@@ -13642,10 +13688,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13656,7 +13702,7 @@
         <v>80</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>79</v>
@@ -13668,13 +13714,13 @@
         <v>79</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>292</v>
+        <v>554</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13701,55 +13747,55 @@
         <v>79</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>157</v>
+        <v>79</v>
       </c>
       <c r="Y96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN96" t="s" s="2">
         <v>558</v>
-      </c>
-      <c r="Z96" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="AA96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF96" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="AG96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH96" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI96" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="AJ96" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL96" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>79</v>
@@ -13760,10 +13806,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13774,7 +13820,7 @@
         <v>80</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>79</v>
@@ -13786,13 +13832,13 @@
         <v>79</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>563</v>
+        <v>105</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>564</v>
+        <v>106</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>565</v>
+        <v>107</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13843,19 +13889,19 @@
         <v>79</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>562</v>
+        <v>108</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>560</v>
+        <v>79</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>79</v>
@@ -13867,7 +13913,7 @@
         <v>79</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>566</v>
+        <v>109</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>79</v>
@@ -13878,21 +13924,21 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>79</v>
@@ -13904,15 +13950,17 @@
         <v>79</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>292</v>
+        <v>112</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>568</v>
+        <v>113</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="N98" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>79</v>
@@ -13937,13 +13985,13 @@
         <v>79</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>157</v>
+        <v>79</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>570</v>
+        <v>79</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>571</v>
+        <v>79</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>79</v>
@@ -13961,19 +14009,19 @@
         <v>79</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>567</v>
+        <v>119</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>79</v>
@@ -13985,7 +14033,7 @@
         <v>79</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>572</v>
+        <v>109</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>79</v>
@@ -13996,14 +14044,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>79</v>
+        <v>562</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14016,24 +14064,26 @@
         <v>79</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>543</v>
+        <v>112</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>574</v>
+        <v>563</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>575</v>
+        <v>564</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="O99" s="2"/>
+        <v>115</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>79</v>
       </c>
@@ -14081,7 +14131,7 @@
         <v>79</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14093,7 +14143,7 @@
         <v>79</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>577</v>
+        <v>120</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>79</v>
@@ -14105,7 +14155,7 @@
         <v>79</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>578</v>
+        <v>190</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>79</v>
@@ -14116,10 +14166,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>579</v>
+        <v>566</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>579</v>
+        <v>566</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14142,13 +14192,13 @@
         <v>79</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>105</v>
+        <v>292</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>106</v>
+        <v>567</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>107</v>
+        <v>568</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -14175,13 +14225,13 @@
         <v>79</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>79</v>
+        <v>157</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>79</v>
+        <v>569</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>79</v>
+        <v>570</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>79</v>
@@ -14199,7 +14249,7 @@
         <v>79</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>108</v>
+        <v>566</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14208,22 +14258,22 @@
         <v>91</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>79</v>
+        <v>571</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>79</v>
+        <v>572</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>79</v>
+        <v>301</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>109</v>
+        <v>418</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>79</v>
@@ -14234,14 +14284,14 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -14260,17 +14310,15 @@
         <v>79</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>112</v>
+        <v>574</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>113</v>
+        <v>575</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>576</v>
+      </c>
+      <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>79</v>
@@ -14319,7 +14367,7 @@
         <v>79</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>119</v>
+        <v>573</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14328,10 +14376,10 @@
         <v>81</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>79</v>
+        <v>571</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>79</v>
@@ -14343,7 +14391,7 @@
         <v>79</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>109</v>
+        <v>577</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>79</v>
@@ -14354,46 +14402,42 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>551</v>
+        <v>79</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I102" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>112</v>
+        <v>292</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>552</v>
+        <v>579</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>580</v>
+      </c>
+      <c r="N102" s="2"/>
+      <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>79</v>
       </c>
@@ -14417,13 +14461,13 @@
         <v>79</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>79</v>
+        <v>157</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>79</v>
+        <v>581</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>79</v>
+        <v>582</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>79</v>
@@ -14441,19 +14485,19 @@
         <v>79</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>554</v>
+        <v>578</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>79</v>
@@ -14465,7 +14509,7 @@
         <v>79</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>190</v>
+        <v>583</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>79</v>
@@ -14476,10 +14520,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14499,18 +14543,20 @@
         <v>79</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>292</v>
+        <v>554</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="N103" s="2"/>
+        <v>586</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>587</v>
+      </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>79</v>
@@ -14535,13 +14581,13 @@
         <v>79</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>157</v>
+        <v>79</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>585</v>
+        <v>79</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>586</v>
+        <v>79</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>79</v>
@@ -14559,7 +14605,7 @@
         <v>79</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14568,16 +14614,16 @@
         <v>81</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>587</v>
+        <v>79</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>103</v>
+        <v>588</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>588</v>
+        <v>79</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>320</v>
+        <v>79</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>79</v>
@@ -14586,7 +14632,7 @@
         <v>589</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>590</v>
+        <v>79</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>79</v>
@@ -14594,10 +14640,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14608,7 +14654,7 @@
         <v>80</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>79</v>
@@ -14617,16 +14663,16 @@
         <v>79</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>592</v>
+        <v>105</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>593</v>
+        <v>106</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>594</v>
+        <v>107</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14677,19 +14723,19 @@
         <v>79</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>591</v>
+        <v>108</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>587</v>
+        <v>79</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>79</v>
@@ -14701,10 +14747,10 @@
         <v>79</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>566</v>
+        <v>109</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>590</v>
+        <v>79</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>79</v>
@@ -14712,14 +14758,14 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -14738,15 +14784,17 @@
         <v>79</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>596</v>
+        <v>112</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>597</v>
+        <v>113</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="N105" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>79</v>
@@ -14795,7 +14843,7 @@
         <v>79</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>595</v>
+        <v>119</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -14807,29 +14855,505 @@
         <v>79</v>
       </c>
       <c r="AJ105" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AO105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP105" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="106" hidden="true">
+      <c r="A106" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="P106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AO106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP106" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="107" hidden="true">
+      <c r="A107" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="N107" s="2"/>
+      <c r="O107" s="2"/>
+      <c r="P107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q107" s="2"/>
+      <c r="R107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="AK105" t="s" s="2">
+      <c r="AK107" t="s" s="2">
         <v>599</v>
       </c>
-      <c r="AL105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM105" t="s" s="2">
+      <c r="AL107" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN107" t="s" s="2">
         <v>600</v>
       </c>
-      <c r="AN105" t="s" s="2">
+      <c r="AO107" t="s" s="2">
         <v>601</v>
       </c>
-      <c r="AO105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP105" t="s" s="2">
+      <c r="AP107" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="108" hidden="true">
+      <c r="A108" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E108" s="2"/>
+      <c r="F108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="N108" s="2"/>
+      <c r="O108" s="2"/>
+      <c r="P108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q108" s="2"/>
+      <c r="R108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN108" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="AO108" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AP108" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="109" hidden="true">
+      <c r="A109" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E109" s="2"/>
+      <c r="F109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="N109" s="2"/>
+      <c r="O109" s="2"/>
+      <c r="P109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q109" s="2"/>
+      <c r="R109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF109" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="AG109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="AN109" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="AO109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP109" t="s" s="2">
         <v>79</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP105">
+  <autoFilter ref="A1:AP109">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -14839,7 +15363,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI104">
+  <conditionalFormatting sqref="A2:AI108">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
